--- a/video_list.xlsx
+++ b/video_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,33 +426,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>video_1.mp4</t>
+          <t>video_2.mp4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>video_2.mp4</t>
+          <t>video_3.mp4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>video_3.mp4</t>
+          <t>video_4.mp4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
-        <is>
-          <t>video_4.mp4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
         <is>
           <t>video_5.mp4</t>
         </is>

--- a/video_list.xlsx
+++ b/video_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -423,34 +423,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>video_2.mp4</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>video_3.mp4</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>video_4.mp4</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>video_5.mp4</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/video_list.xlsx
+++ b/video_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -423,6 +423,41 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>video_11.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>video_14.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>video_17.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>video_19.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>video_23.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/video_list.xlsx
+++ b/video_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,35 +426,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>video_11.mp4</t>
+          <t>video_124.mp4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>video_14.mp4</t>
+          <t>video_125.mp4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>video_17.mp4</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>video_19.mp4</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>video_23.mp4</t>
+          <t>video_130.mp4</t>
         </is>
       </c>
     </row>
